--- a/results/Int Task Remove ACC -0.4/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_6_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7562092325114987</v>
+        <v>0.7677281239521451</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7605675182366302</v>
+        <v>0.7574808934525279</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7625525113721918</v>
+        <v>0.7538667824447522</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7666913406849254</v>
+        <v>0.7553270572753557</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7703714863248999</v>
+        <v>0.7552792118232834</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7777400813609936</v>
+        <v>0.7608585451186567</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7777400813609936</v>
+        <v>0.7643643118795908</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7843281233194779</v>
+        <v>0.772377436559303</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.786555111634116</v>
+        <v>0.7737898659378342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7936271439507532</v>
+        <v>0.7748491879717325</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7869434110881242</v>
+        <v>0.7753612529339938</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8072393727738025</v>
+        <v>0.7737293671430651</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8029063937340648</v>
+        <v>0.7631515680654937</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.814291634242476</v>
+        <v>0.7554844332251472</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.814291634242476</v>
+        <v>0.7375645320477537</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7814554191103436</v>
+        <v>0.7369314694959541</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.72153235143394</v>
+        <v>0.7360916038744536</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7260974402287724</v>
+        <v>0.7169633084695149</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7260974402287724</v>
+        <v>0.6916479239027971</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7050573038257382</v>
+        <v>0.6783690315764167</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7050573038257382</v>
+        <v>0.673289109900608</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7133503837126174</v>
+        <v>0.6705374032810119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7173682154358128</v>
+        <v>0.6670063298346841</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7075318231568825</v>
+        <v>0.6851963007952626</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6905079368092066</v>
+        <v>0.6851160311525297</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6929318427695637</v>
+        <v>0.6851160311525297</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6771503565079304</v>
+        <v>0.696235551464308</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6895893832128103</v>
+        <v>0.696235551464308</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6637069707264918</v>
+        <v>0.6958697907769785</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6637069707264918</v>
+        <v>0.7221994198442374</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6897637620918506</v>
+        <v>0.7187414985353755</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6965811458867146</v>
+        <v>0.7468916272831375</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7605698907383858</v>
+        <v>0.7531969461157402</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7654528947684754</v>
+        <v>0.7366246259355566</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7255078735424931</v>
+        <v>0.7296130924136883</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7152804138908396</v>
+        <v>0.7264307767254414</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6931034537298891</v>
+        <v>0.7110585470166582</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6292606177361905</v>
+        <v>0.7117647617059237</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6263048759656082</v>
+        <v>0.7085389501521564</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6619746490279069</v>
+        <v>0.6728201453869076</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6622573721537888</v>
+        <v>0.6788356235883615</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6777055219187529</v>
+        <v>0.6631158223723752</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6652285351857827</v>
+        <v>0.6701653159223337</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5625102808409411</v>
+        <v>0.6493727105358058</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5533520286471678</v>
+        <v>0.6469867646035392</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5804626062089953</v>
+        <v>0.6125874662313917</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5798773891092679</v>
+        <v>0.6410555102144109</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5888458411625891</v>
+        <v>0.628018613067107</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5966972403059578</v>
+        <v>0.6188180512586913</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5959151055605114</v>
+        <v>0.5693407133954612</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5979803683388059</v>
+        <v>0.5500815349770025</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5442515073294487</v>
+        <v>0.5381363840542576</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5488545561523716</v>
+        <v>0.5224561245341988</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5136869626283523</v>
+        <v>0.5334151055605114</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5124587975528435</v>
+        <v>0.492610843282024</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5124587975528435</v>
+        <v>0.5022530858339502</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5070158831084202</v>
+        <v>0.4934859010129001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5320782008212019</v>
+        <v>0.5365218966095369</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5108901784753987</v>
+        <v>0.5387911945388173</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5015350086359064</v>
+        <v>0.5807647047658815</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4879453185795358</v>
+        <v>0.565820316207034</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4902735336357482</v>
+        <v>0.5960764356798958</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4858294424304541</v>
+        <v>0.5960764356798958</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4853201453869076</v>
+        <v>0.5945908541638987</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4844071276279411</v>
+        <v>0.5956980216498693</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4712690037390628</v>
+        <v>0.5956980216498693</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5089629162158914</v>
+        <v>0.5757777060755025</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5089629162158914</v>
+        <v>0.5992472842763237</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.513913536546017</v>
+        <v>0.6289379574974219</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5081428214423546</v>
+        <v>0.6100457260171706</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5185193532876547</v>
+        <v>0.6008775883994155</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5173742257735937</v>
+        <v>0.5983832982203073</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.51681431535926</v>
+        <v>0.5987969043597092</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4885953840605842</v>
+        <v>0.5879968809510252</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4928030159242318</v>
+        <v>0.590847046393481</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4948006624024902</v>
+        <v>0.5791367731445455</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4607742422229392</v>
+        <v>0.5608708821277861</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.454521118428961</v>
+        <v>0.5649365593030539</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.454992455444417</v>
+        <v>0.5649365593030539</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4467120289002348</v>
+        <v>0.562974104934171</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4625820885607455</v>
+        <v>0.5797520419331776</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4625820885607455</v>
+        <v>0.5282687538355445</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4584685659334055</v>
+        <v>0.548822131961711</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4829994432529213</v>
+        <v>0.5311691372318282</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4702073092034088</v>
+        <v>0.5135276095937644</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5085754075958016</v>
+        <v>0.5322933076470476</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5016144874447207</v>
+        <v>0.5322933076470476</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5020759390361949</v>
+        <v>0.5028205091705101</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5033321787158123</v>
+        <v>0.5008481693776453</v>
       </c>
     </row>
   </sheetData>
